--- a/app/templates_excel/albedo/a7_hermetic_en.xlsx
+++ b/app/templates_excel/albedo/a7_hermetic_en.xlsx
@@ -1244,10 +1244,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A window at an open grave.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A bridge being built across a gorge.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1504,10 +1500,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Chinese woman nusing a baby with a message.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>One hand slightly flexed with a very prominent thumb.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1632,10 +1624,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A pagent.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Sunshine just after a storm.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2396,10 +2384,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A tree feiled and sawed.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Butterfly emerging from a chrysalis.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2476,10 +2460,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A gigatic tent.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A master instructing his pupil.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2500,10 +2480,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>An inhibited island.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>The purging of the priesthood.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2625,6 +2601,30 @@
   </si>
   <si>
     <t>A professor peering over his glasses.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A tree felled and sawed.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A gigantic tent.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chinese woman nursing a baby with a message.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A widow at an open grave.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A pageant.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>An inhabited island.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10313,12 +10313,12 @@
         <v>12</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="M9" s="7" t="s">
         <v>359</v>
@@ -10326,7 +10326,7 @@
     </row>
     <row r="10" spans="1:17" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="M10" s="7" t="s">
         <v>360</v>
@@ -10558,42 +10558,42 @@
     </row>
     <row r="39" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A40" s="9" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="M40" s="7" t="s">
         <v>389</v>
@@ -10601,7 +10601,7 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A41" s="9" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="M41" s="7" t="s">
         <v>390</v>
@@ -10628,7 +10628,7 @@
         <v>45</v>
       </c>
       <c r="M44" s="7" t="s">
-        <v>393</v>
+        <v>736</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.4">
@@ -10636,7 +10636,7 @@
         <v>46</v>
       </c>
       <c r="M45" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.4">
@@ -10644,7 +10644,7 @@
         <v>47</v>
       </c>
       <c r="M46" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.4">
@@ -10652,7 +10652,7 @@
         <v>48</v>
       </c>
       <c r="M47" s="7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.4">
@@ -10660,7 +10660,7 @@
         <v>49</v>
       </c>
       <c r="M48" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.4">
@@ -10668,7 +10668,7 @@
         <v>50</v>
       </c>
       <c r="M49" s="7" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.4">
@@ -10676,7 +10676,7 @@
         <v>51</v>
       </c>
       <c r="M50" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.4">
@@ -10684,7 +10684,7 @@
         <v>52</v>
       </c>
       <c r="M51" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.4">
@@ -10692,7 +10692,7 @@
         <v>53</v>
       </c>
       <c r="M52" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.4">
@@ -10700,7 +10700,7 @@
         <v>54</v>
       </c>
       <c r="M53" s="7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.4">
@@ -10708,7 +10708,7 @@
         <v>55</v>
       </c>
       <c r="M54" s="7" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.4">
@@ -10716,7 +10716,7 @@
         <v>56</v>
       </c>
       <c r="M55" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.4">
@@ -10724,7 +10724,7 @@
         <v>57</v>
       </c>
       <c r="M56" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.4">
@@ -10732,7 +10732,7 @@
         <v>58</v>
       </c>
       <c r="M57" s="7" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.4">
@@ -10740,7 +10740,7 @@
         <v>59</v>
       </c>
       <c r="M58" s="7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.4">
@@ -10748,7 +10748,7 @@
         <v>60</v>
       </c>
       <c r="M59" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.4">
@@ -10756,7 +10756,7 @@
         <v>61</v>
       </c>
       <c r="M60" s="7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.4">
@@ -10764,7 +10764,7 @@
         <v>62</v>
       </c>
       <c r="M61" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.4">
@@ -10772,7 +10772,7 @@
         <v>63</v>
       </c>
       <c r="M62" s="7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.4">
@@ -10780,7 +10780,7 @@
         <v>64</v>
       </c>
       <c r="M63" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.4">
@@ -10788,7 +10788,7 @@
         <v>65</v>
       </c>
       <c r="M64" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.4">
@@ -10796,7 +10796,7 @@
         <v>66</v>
       </c>
       <c r="M65" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.4">
@@ -10804,7 +10804,7 @@
         <v>67</v>
       </c>
       <c r="M66" s="7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.4">
@@ -10812,7 +10812,7 @@
         <v>68</v>
       </c>
       <c r="M67" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.4">
@@ -10820,7 +10820,7 @@
         <v>69</v>
       </c>
       <c r="M68" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.4">
@@ -10828,58 +10828,58 @@
         <v>70</v>
       </c>
       <c r="M69" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="70" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B70" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="K70" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="L70" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A71" s="10" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="M71" s="7" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A72" s="10" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="M72" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.4">
@@ -10887,7 +10887,7 @@
         <v>71</v>
       </c>
       <c r="M73" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.4">
@@ -10895,7 +10895,7 @@
         <v>72</v>
       </c>
       <c r="M74" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.4">
@@ -10903,7 +10903,7 @@
         <v>73</v>
       </c>
       <c r="M75" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.4">
@@ -10911,7 +10911,7 @@
         <v>74</v>
       </c>
       <c r="M76" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.4">
@@ -10919,7 +10919,7 @@
         <v>75</v>
       </c>
       <c r="M77" s="7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.4">
@@ -10927,7 +10927,7 @@
         <v>76</v>
       </c>
       <c r="M78" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.4">
@@ -10935,7 +10935,7 @@
         <v>77</v>
       </c>
       <c r="M79" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.4">
@@ -10943,7 +10943,7 @@
         <v>78</v>
       </c>
       <c r="M80" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.4">
@@ -10951,7 +10951,7 @@
         <v>79</v>
       </c>
       <c r="M81" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.4">
@@ -10959,7 +10959,7 @@
         <v>80</v>
       </c>
       <c r="M82" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.4">
@@ -10967,7 +10967,7 @@
         <v>81</v>
       </c>
       <c r="M83" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.4">
@@ -10975,7 +10975,7 @@
         <v>82</v>
       </c>
       <c r="M84" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.4">
@@ -10983,7 +10983,7 @@
         <v>83</v>
       </c>
       <c r="M85" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.4">
@@ -10991,7 +10991,7 @@
         <v>84</v>
       </c>
       <c r="M86" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.4">
@@ -10999,7 +10999,7 @@
         <v>85</v>
       </c>
       <c r="M87" s="7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.4">
@@ -11007,7 +11007,7 @@
         <v>86</v>
       </c>
       <c r="M88" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.4">
@@ -11015,7 +11015,7 @@
         <v>87</v>
       </c>
       <c r="M89" s="7" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.4">
@@ -11023,7 +11023,7 @@
         <v>88</v>
       </c>
       <c r="M90" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.4">
@@ -11031,7 +11031,7 @@
         <v>89</v>
       </c>
       <c r="M91" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.4">
@@ -11039,7 +11039,7 @@
         <v>90</v>
       </c>
       <c r="M92" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.4">
@@ -11047,7 +11047,7 @@
         <v>91</v>
       </c>
       <c r="M93" s="7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.4">
@@ -11055,7 +11055,7 @@
         <v>92</v>
       </c>
       <c r="M94" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.4">
@@ -11063,7 +11063,7 @@
         <v>93</v>
       </c>
       <c r="M95" s="7" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.4">
@@ -11071,7 +11071,7 @@
         <v>94</v>
       </c>
       <c r="M96" s="7" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.4">
@@ -11079,7 +11079,7 @@
         <v>95</v>
       </c>
       <c r="M97" s="7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.4">
@@ -11087,7 +11087,7 @@
         <v>96</v>
       </c>
       <c r="M98" s="7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.4">
@@ -11095,7 +11095,7 @@
         <v>97</v>
       </c>
       <c r="M99" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.4">
@@ -11103,50 +11103,50 @@
         <v>98</v>
       </c>
       <c r="M100" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="101" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B101" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J101" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="L101" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A102" s="11" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="M102" s="7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.4">
@@ -11154,7 +11154,7 @@
         <v>99</v>
       </c>
       <c r="M103" s="7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.4">
@@ -11162,7 +11162,7 @@
         <v>100</v>
       </c>
       <c r="M104" s="7" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.4">
@@ -11170,7 +11170,7 @@
         <v>101</v>
       </c>
       <c r="M105" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.4">
@@ -11178,7 +11178,7 @@
         <v>102</v>
       </c>
       <c r="M106" s="7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.4">
@@ -11186,7 +11186,7 @@
         <v>103</v>
       </c>
       <c r="M107" s="7" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.4">
@@ -11194,7 +11194,7 @@
         <v>104</v>
       </c>
       <c r="M108" s="7" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.4">
@@ -11202,7 +11202,7 @@
         <v>105</v>
       </c>
       <c r="M109" s="7" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.4">
@@ -11210,7 +11210,7 @@
         <v>106</v>
       </c>
       <c r="M110" s="7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.4">
@@ -11218,7 +11218,7 @@
         <v>107</v>
       </c>
       <c r="M111" s="7" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.4">
@@ -11226,7 +11226,7 @@
         <v>108</v>
       </c>
       <c r="M112" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.4">
@@ -11234,7 +11234,7 @@
         <v>109</v>
       </c>
       <c r="M113" s="7" t="s">
-        <v>458</v>
+        <v>735</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.4">
@@ -11242,7 +11242,7 @@
         <v>110</v>
       </c>
       <c r="M114" s="7" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.4">
@@ -11250,7 +11250,7 @@
         <v>111</v>
       </c>
       <c r="M115" s="7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.4">
@@ -11258,7 +11258,7 @@
         <v>112</v>
       </c>
       <c r="M116" s="7" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.4">
@@ -11266,7 +11266,7 @@
         <v>113</v>
       </c>
       <c r="M117" s="7" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.4">
@@ -11274,7 +11274,7 @@
         <v>114</v>
       </c>
       <c r="M118" s="7" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.4">
@@ -11282,7 +11282,7 @@
         <v>115</v>
       </c>
       <c r="M119" s="7" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.4">
@@ -11290,7 +11290,7 @@
         <v>116</v>
       </c>
       <c r="M120" s="7" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.4">
@@ -11298,7 +11298,7 @@
         <v>117</v>
       </c>
       <c r="M121" s="7" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.4">
@@ -11306,7 +11306,7 @@
         <v>118</v>
       </c>
       <c r="M122" s="7" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.4">
@@ -11314,7 +11314,7 @@
         <v>119</v>
       </c>
       <c r="M123" s="7" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.4">
@@ -11322,7 +11322,7 @@
         <v>120</v>
       </c>
       <c r="M124" s="7" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.4">
@@ -11330,7 +11330,7 @@
         <v>121</v>
       </c>
       <c r="M125" s="7" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.4">
@@ -11338,7 +11338,7 @@
         <v>122</v>
       </c>
       <c r="M126" s="7" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.4">
@@ -11346,7 +11346,7 @@
         <v>123</v>
       </c>
       <c r="M127" s="7" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.4">
@@ -11354,7 +11354,7 @@
         <v>124</v>
       </c>
       <c r="M128" s="7" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.4">
@@ -11362,7 +11362,7 @@
         <v>125</v>
       </c>
       <c r="M129" s="7" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.4">
@@ -11370,7 +11370,7 @@
         <v>126</v>
       </c>
       <c r="M130" s="7" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.4">
@@ -11378,50 +11378,50 @@
         <v>127</v>
       </c>
       <c r="M131" s="7" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="132" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B132" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="H132" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="I132" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J132" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="K132" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="L132" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A133" s="6" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="M133" s="7" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.4">
@@ -11429,7 +11429,7 @@
         <v>128</v>
       </c>
       <c r="M134" s="7" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.4">
@@ -11437,7 +11437,7 @@
         <v>129</v>
       </c>
       <c r="M135" s="7" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.4">
@@ -11445,7 +11445,7 @@
         <v>130</v>
       </c>
       <c r="M136" s="7" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.4">
@@ -11453,7 +11453,7 @@
         <v>131</v>
       </c>
       <c r="M137" s="7" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.4">
@@ -11461,7 +11461,7 @@
         <v>132</v>
       </c>
       <c r="M138" s="7" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.4">
@@ -11469,7 +11469,7 @@
         <v>133</v>
       </c>
       <c r="M139" s="7" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.4">
@@ -11477,7 +11477,7 @@
         <v>134</v>
       </c>
       <c r="M140" s="7" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.4">
@@ -11485,7 +11485,7 @@
         <v>135</v>
       </c>
       <c r="M141" s="7" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.4">
@@ -11493,7 +11493,7 @@
         <v>136</v>
       </c>
       <c r="M142" s="7" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.4">
@@ -11501,7 +11501,7 @@
         <v>137</v>
       </c>
       <c r="M143" s="7" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.4">
@@ -11509,7 +11509,7 @@
         <v>138</v>
       </c>
       <c r="M144" s="7" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.4">
@@ -11517,7 +11517,7 @@
         <v>139</v>
       </c>
       <c r="M145" s="7" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.4">
@@ -11525,7 +11525,7 @@
         <v>140</v>
       </c>
       <c r="M146" s="7" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.4">
@@ -11533,7 +11533,7 @@
         <v>141</v>
       </c>
       <c r="M147" s="7" t="s">
-        <v>490</v>
+        <v>737</v>
       </c>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.4">
@@ -11541,7 +11541,7 @@
         <v>142</v>
       </c>
       <c r="M148" s="7" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.4">
@@ -11549,7 +11549,7 @@
         <v>143</v>
       </c>
       <c r="M149" s="7" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.4">
@@ -11557,7 +11557,7 @@
         <v>144</v>
       </c>
       <c r="M150" s="7" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.4">
@@ -11565,7 +11565,7 @@
         <v>145</v>
       </c>
       <c r="M151" s="7" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.4">
@@ -11573,7 +11573,7 @@
         <v>146</v>
       </c>
       <c r="M152" s="7" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.4">
@@ -11581,7 +11581,7 @@
         <v>147</v>
       </c>
       <c r="M153" s="7" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="154" spans="1:13" x14ac:dyDescent="0.4">
@@ -11589,7 +11589,7 @@
         <v>148</v>
       </c>
       <c r="M154" s="7" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.4">
@@ -11597,7 +11597,7 @@
         <v>149</v>
       </c>
       <c r="M155" s="7" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.4">
@@ -11605,7 +11605,7 @@
         <v>150</v>
       </c>
       <c r="M156" s="7" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.4">
@@ -11613,7 +11613,7 @@
         <v>151</v>
       </c>
       <c r="M157" s="7" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.4">
@@ -11621,7 +11621,7 @@
         <v>152</v>
       </c>
       <c r="M158" s="7" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.4">
@@ -11629,7 +11629,7 @@
         <v>153</v>
       </c>
       <c r="M159" s="7" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="160" spans="1:13" x14ac:dyDescent="0.4">
@@ -11637,7 +11637,7 @@
         <v>154</v>
       </c>
       <c r="M160" s="7" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.4">
@@ -11645,7 +11645,7 @@
         <v>155</v>
       </c>
       <c r="M161" s="7" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="162" spans="1:13" x14ac:dyDescent="0.4">
@@ -11653,58 +11653,58 @@
         <v>156</v>
       </c>
       <c r="M162" s="7" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="163" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B163" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F163" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="H163" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="I163" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J163" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="K163" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="L163" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A164" s="9" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="M164" s="7" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A165" s="9" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="M165" s="7" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.4">
@@ -11712,7 +11712,7 @@
         <v>157</v>
       </c>
       <c r="M166" s="7" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.4">
@@ -11720,7 +11720,7 @@
         <v>158</v>
       </c>
       <c r="M167" s="7" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="168" spans="1:13" x14ac:dyDescent="0.4">
@@ -11728,7 +11728,7 @@
         <v>159</v>
       </c>
       <c r="M168" s="7" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.4">
@@ -11736,7 +11736,7 @@
         <v>160</v>
       </c>
       <c r="M169" s="7" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.4">
@@ -11744,7 +11744,7 @@
         <v>161</v>
       </c>
       <c r="M170" s="7" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.4">
@@ -11752,7 +11752,7 @@
         <v>162</v>
       </c>
       <c r="M171" s="7" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.4">
@@ -11760,7 +11760,7 @@
         <v>163</v>
       </c>
       <c r="M172" s="7" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.4">
@@ -11768,7 +11768,7 @@
         <v>164</v>
       </c>
       <c r="M173" s="7" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.4">
@@ -11776,7 +11776,7 @@
         <v>165</v>
       </c>
       <c r="M174" s="7" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.4">
@@ -11784,7 +11784,7 @@
         <v>166</v>
       </c>
       <c r="M175" s="7" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.4">
@@ -11792,7 +11792,7 @@
         <v>167</v>
       </c>
       <c r="M176" s="7" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.4">
@@ -11800,7 +11800,7 @@
         <v>168</v>
       </c>
       <c r="M177" s="7" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="178" spans="1:13" x14ac:dyDescent="0.4">
@@ -11808,7 +11808,7 @@
         <v>169</v>
       </c>
       <c r="M178" s="7" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.4">
@@ -11816,7 +11816,7 @@
         <v>170</v>
       </c>
       <c r="M179" s="7" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.4">
@@ -11824,7 +11824,7 @@
         <v>171</v>
       </c>
       <c r="M180" s="7" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.4">
@@ -11832,7 +11832,7 @@
         <v>172</v>
       </c>
       <c r="M181" s="7" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="182" spans="1:13" x14ac:dyDescent="0.4">
@@ -11840,7 +11840,7 @@
         <v>173</v>
       </c>
       <c r="M182" s="7" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="183" spans="1:13" x14ac:dyDescent="0.4">
@@ -11848,7 +11848,7 @@
         <v>174</v>
       </c>
       <c r="M183" s="7" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.4">
@@ -11856,7 +11856,7 @@
         <v>175</v>
       </c>
       <c r="M184" s="7" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.4">
@@ -11864,7 +11864,7 @@
         <v>176</v>
       </c>
       <c r="M185" s="7" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.4">
@@ -11872,7 +11872,7 @@
         <v>177</v>
       </c>
       <c r="M186" s="7" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.4">
@@ -11880,7 +11880,7 @@
         <v>178</v>
       </c>
       <c r="M187" s="7" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="188" spans="1:13" x14ac:dyDescent="0.4">
@@ -11888,7 +11888,7 @@
         <v>179</v>
       </c>
       <c r="M188" s="7" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="189" spans="1:13" x14ac:dyDescent="0.4">
@@ -11896,7 +11896,7 @@
         <v>180</v>
       </c>
       <c r="M189" s="7" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.4">
@@ -11904,7 +11904,7 @@
         <v>181</v>
       </c>
       <c r="M190" s="7" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.4">
@@ -11912,7 +11912,7 @@
         <v>182</v>
       </c>
       <c r="M191" s="7" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="192" spans="1:13" x14ac:dyDescent="0.4">
@@ -11920,7 +11920,7 @@
         <v>183</v>
       </c>
       <c r="M192" s="7" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.4">
@@ -11928,50 +11928,50 @@
         <v>184</v>
       </c>
       <c r="M193" s="7" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="194" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B194" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D194" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E194" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F194" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G194" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="H194" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="I194" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J194" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="K194" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="L194" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A195" s="10" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="M195" s="7" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.4">
@@ -11979,7 +11979,7 @@
         <v>185</v>
       </c>
       <c r="M196" s="7" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.4">
@@ -11987,7 +11987,7 @@
         <v>186</v>
       </c>
       <c r="M197" s="7" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.4">
@@ -11995,7 +11995,7 @@
         <v>187</v>
       </c>
       <c r="M198" s="7" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.4">
@@ -12003,7 +12003,7 @@
         <v>188</v>
       </c>
       <c r="M199" s="7" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.4">
@@ -12011,7 +12011,7 @@
         <v>189</v>
       </c>
       <c r="M200" s="7" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="201" spans="1:13" x14ac:dyDescent="0.4">
@@ -12019,7 +12019,7 @@
         <v>190</v>
       </c>
       <c r="M201" s="7" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="202" spans="1:13" x14ac:dyDescent="0.4">
@@ -12027,7 +12027,7 @@
         <v>191</v>
       </c>
       <c r="M202" s="7" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="203" spans="1:13" x14ac:dyDescent="0.4">
@@ -12035,7 +12035,7 @@
         <v>192</v>
       </c>
       <c r="M203" s="7" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="204" spans="1:13" x14ac:dyDescent="0.4">
@@ -12043,7 +12043,7 @@
         <v>193</v>
       </c>
       <c r="M204" s="7" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.4">
@@ -12051,7 +12051,7 @@
         <v>194</v>
       </c>
       <c r="M205" s="7" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
     </row>
     <row r="206" spans="1:13" x14ac:dyDescent="0.4">
@@ -12059,7 +12059,7 @@
         <v>195</v>
       </c>
       <c r="M206" s="7" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="207" spans="1:13" x14ac:dyDescent="0.4">
@@ -12067,7 +12067,7 @@
         <v>196</v>
       </c>
       <c r="M207" s="7" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="208" spans="1:13" x14ac:dyDescent="0.4">
@@ -12075,7 +12075,7 @@
         <v>197</v>
       </c>
       <c r="M208" s="7" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="209" spans="1:13" x14ac:dyDescent="0.4">
@@ -12083,7 +12083,7 @@
         <v>198</v>
       </c>
       <c r="M209" s="7" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="210" spans="1:13" x14ac:dyDescent="0.4">
@@ -12091,7 +12091,7 @@
         <v>199</v>
       </c>
       <c r="M210" s="7" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="211" spans="1:13" x14ac:dyDescent="0.4">
@@ -12099,7 +12099,7 @@
         <v>200</v>
       </c>
       <c r="M211" s="7" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="212" spans="1:13" x14ac:dyDescent="0.4">
@@ -12107,7 +12107,7 @@
         <v>201</v>
       </c>
       <c r="M212" s="7" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.4">
@@ -12115,7 +12115,7 @@
         <v>202</v>
       </c>
       <c r="M213" s="7" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="214" spans="1:13" x14ac:dyDescent="0.4">
@@ -12123,7 +12123,7 @@
         <v>203</v>
       </c>
       <c r="M214" s="7" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="215" spans="1:13" x14ac:dyDescent="0.4">
@@ -12131,7 +12131,7 @@
         <v>204</v>
       </c>
       <c r="M215" s="7" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="216" spans="1:13" x14ac:dyDescent="0.4">
@@ -12139,7 +12139,7 @@
         <v>205</v>
       </c>
       <c r="M216" s="7" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="217" spans="1:13" x14ac:dyDescent="0.4">
@@ -12147,7 +12147,7 @@
         <v>206</v>
       </c>
       <c r="M217" s="7" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="218" spans="1:13" x14ac:dyDescent="0.4">
@@ -12155,7 +12155,7 @@
         <v>207</v>
       </c>
       <c r="M218" s="7" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="219" spans="1:13" x14ac:dyDescent="0.4">
@@ -12163,7 +12163,7 @@
         <v>208</v>
       </c>
       <c r="M219" s="7" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="220" spans="1:13" x14ac:dyDescent="0.4">
@@ -12171,7 +12171,7 @@
         <v>209</v>
       </c>
       <c r="M220" s="7" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="221" spans="1:13" x14ac:dyDescent="0.4">
@@ -12179,7 +12179,7 @@
         <v>210</v>
       </c>
       <c r="M221" s="7" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="222" spans="1:13" x14ac:dyDescent="0.4">
@@ -12187,7 +12187,7 @@
         <v>211</v>
       </c>
       <c r="M222" s="7" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="223" spans="1:13" x14ac:dyDescent="0.4">
@@ -12195,7 +12195,7 @@
         <v>212</v>
       </c>
       <c r="M223" s="7" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="224" spans="1:13" x14ac:dyDescent="0.4">
@@ -12203,50 +12203,50 @@
         <v>213</v>
       </c>
       <c r="M224" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="225" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B225" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D225" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E225" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F225" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G225" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="H225" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="I225" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J225" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="K225" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="L225" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A226" s="11" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="M226" s="7" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.4">
@@ -12254,7 +12254,7 @@
         <v>214</v>
       </c>
       <c r="M227" s="7" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.4">
@@ -12262,7 +12262,7 @@
         <v>215</v>
       </c>
       <c r="M228" s="7" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="229" spans="1:13" x14ac:dyDescent="0.4">
@@ -12270,7 +12270,7 @@
         <v>216</v>
       </c>
       <c r="M229" s="7" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.4">
@@ -12278,7 +12278,7 @@
         <v>217</v>
       </c>
       <c r="M230" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
     </row>
     <row r="231" spans="1:13" x14ac:dyDescent="0.4">
@@ -12286,7 +12286,7 @@
         <v>218</v>
       </c>
       <c r="M231" s="7" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="232" spans="1:13" x14ac:dyDescent="0.4">
@@ -12294,7 +12294,7 @@
         <v>219</v>
       </c>
       <c r="M232" s="7" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.4">
@@ -12302,7 +12302,7 @@
         <v>220</v>
       </c>
       <c r="M233" s="7" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.4">
@@ -12310,7 +12310,7 @@
         <v>221</v>
       </c>
       <c r="M234" s="7" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.4">
@@ -12318,7 +12318,7 @@
         <v>222</v>
       </c>
       <c r="M235" s="7" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="236" spans="1:13" x14ac:dyDescent="0.4">
@@ -12326,7 +12326,7 @@
         <v>223</v>
       </c>
       <c r="M236" s="7" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="237" spans="1:13" x14ac:dyDescent="0.4">
@@ -12334,7 +12334,7 @@
         <v>224</v>
       </c>
       <c r="M237" s="7" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="238" spans="1:13" x14ac:dyDescent="0.4">
@@ -12342,7 +12342,7 @@
         <v>225</v>
       </c>
       <c r="M238" s="7" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="239" spans="1:13" x14ac:dyDescent="0.4">
@@ -12350,7 +12350,7 @@
         <v>226</v>
       </c>
       <c r="M239" s="7" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="240" spans="1:13" x14ac:dyDescent="0.4">
@@ -12358,7 +12358,7 @@
         <v>227</v>
       </c>
       <c r="M240" s="7" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.4">
@@ -12366,7 +12366,7 @@
         <v>228</v>
       </c>
       <c r="M241" s="7" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="242" spans="1:13" x14ac:dyDescent="0.4">
@@ -12374,7 +12374,7 @@
         <v>229</v>
       </c>
       <c r="M242" s="7" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="243" spans="1:13" x14ac:dyDescent="0.4">
@@ -12382,7 +12382,7 @@
         <v>230</v>
       </c>
       <c r="M243" s="7" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="244" spans="1:13" x14ac:dyDescent="0.4">
@@ -12390,7 +12390,7 @@
         <v>231</v>
       </c>
       <c r="M244" s="7" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="245" spans="1:13" x14ac:dyDescent="0.4">
@@ -12398,7 +12398,7 @@
         <v>232</v>
       </c>
       <c r="M245" s="7" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="246" spans="1:13" x14ac:dyDescent="0.4">
@@ -12406,7 +12406,7 @@
         <v>233</v>
       </c>
       <c r="M246" s="7" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="247" spans="1:13" x14ac:dyDescent="0.4">
@@ -12414,7 +12414,7 @@
         <v>234</v>
       </c>
       <c r="M247" s="7" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="248" spans="1:13" x14ac:dyDescent="0.4">
@@ -12422,7 +12422,7 @@
         <v>235</v>
       </c>
       <c r="M248" s="7" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="249" spans="1:13" x14ac:dyDescent="0.4">
@@ -12430,7 +12430,7 @@
         <v>236</v>
       </c>
       <c r="M249" s="7" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="250" spans="1:13" x14ac:dyDescent="0.4">
@@ -12438,7 +12438,7 @@
         <v>237</v>
       </c>
       <c r="M250" s="7" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="251" spans="1:13" x14ac:dyDescent="0.4">
@@ -12446,7 +12446,7 @@
         <v>238</v>
       </c>
       <c r="M251" s="7" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="252" spans="1:13" x14ac:dyDescent="0.4">
@@ -12454,7 +12454,7 @@
         <v>239</v>
       </c>
       <c r="M252" s="7" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="253" spans="1:13" x14ac:dyDescent="0.4">
@@ -12462,7 +12462,7 @@
         <v>240</v>
       </c>
       <c r="M253" s="7" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="254" spans="1:13" x14ac:dyDescent="0.4">
@@ -12470,7 +12470,7 @@
         <v>241</v>
       </c>
       <c r="M254" s="7" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="255" spans="1:13" x14ac:dyDescent="0.4">
@@ -12478,50 +12478,50 @@
         <v>242</v>
       </c>
       <c r="M255" s="7" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="256" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B256" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C256" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D256" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E256" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F256" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G256" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="H256" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="I256" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J256" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="K256" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="L256" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="257" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A257" s="6" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="M257" s="7" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
     </row>
     <row r="258" spans="1:13" x14ac:dyDescent="0.4">
@@ -12529,7 +12529,7 @@
         <v>243</v>
       </c>
       <c r="M258" s="7" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="259" spans="1:13" x14ac:dyDescent="0.4">
@@ -12537,7 +12537,7 @@
         <v>244</v>
       </c>
       <c r="M259" s="7" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="260" spans="1:13" x14ac:dyDescent="0.4">
@@ -12545,7 +12545,7 @@
         <v>245</v>
       </c>
       <c r="M260" s="7" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="261" spans="1:13" x14ac:dyDescent="0.4">
@@ -12553,7 +12553,7 @@
         <v>246</v>
       </c>
       <c r="M261" s="7" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="262" spans="1:13" x14ac:dyDescent="0.4">
@@ -12561,7 +12561,7 @@
         <v>247</v>
       </c>
       <c r="M262" s="7" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="263" spans="1:13" x14ac:dyDescent="0.4">
@@ -12569,7 +12569,7 @@
         <v>248</v>
       </c>
       <c r="M263" s="7" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="264" spans="1:13" x14ac:dyDescent="0.4">
@@ -12577,7 +12577,7 @@
         <v>249</v>
       </c>
       <c r="M264" s="7" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="265" spans="1:13" x14ac:dyDescent="0.4">
@@ -12585,7 +12585,7 @@
         <v>250</v>
       </c>
       <c r="M265" s="7" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="266" spans="1:13" x14ac:dyDescent="0.4">
@@ -12593,7 +12593,7 @@
         <v>251</v>
       </c>
       <c r="M266" s="7" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="267" spans="1:13" x14ac:dyDescent="0.4">
@@ -12601,7 +12601,7 @@
         <v>252</v>
       </c>
       <c r="M267" s="7" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="268" spans="1:13" x14ac:dyDescent="0.4">
@@ -12609,7 +12609,7 @@
         <v>253</v>
       </c>
       <c r="M268" s="7" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="269" spans="1:13" x14ac:dyDescent="0.4">
@@ -12617,7 +12617,7 @@
         <v>254</v>
       </c>
       <c r="M269" s="7" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="270" spans="1:13" x14ac:dyDescent="0.4">
@@ -12625,7 +12625,7 @@
         <v>255</v>
       </c>
       <c r="M270" s="7" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="271" spans="1:13" x14ac:dyDescent="0.4">
@@ -12633,7 +12633,7 @@
         <v>256</v>
       </c>
       <c r="M271" s="7" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="272" spans="1:13" x14ac:dyDescent="0.4">
@@ -12641,7 +12641,7 @@
         <v>257</v>
       </c>
       <c r="M272" s="7" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="273" spans="1:13" x14ac:dyDescent="0.4">
@@ -12649,7 +12649,7 @@
         <v>258</v>
       </c>
       <c r="M273" s="7" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="274" spans="1:13" x14ac:dyDescent="0.4">
@@ -12657,7 +12657,7 @@
         <v>259</v>
       </c>
       <c r="M274" s="7" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="275" spans="1:13" x14ac:dyDescent="0.4">
@@ -12665,7 +12665,7 @@
         <v>260</v>
       </c>
       <c r="M275" s="7" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="276" spans="1:13" x14ac:dyDescent="0.4">
@@ -12673,7 +12673,7 @@
         <v>261</v>
       </c>
       <c r="M276" s="7" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="277" spans="1:13" x14ac:dyDescent="0.4">
@@ -12681,7 +12681,7 @@
         <v>262</v>
       </c>
       <c r="M277" s="7" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="278" spans="1:13" x14ac:dyDescent="0.4">
@@ -12689,7 +12689,7 @@
         <v>263</v>
       </c>
       <c r="M278" s="7" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="279" spans="1:13" x14ac:dyDescent="0.4">
@@ -12697,7 +12697,7 @@
         <v>264</v>
       </c>
       <c r="M279" s="7" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="280" spans="1:13" x14ac:dyDescent="0.4">
@@ -12705,7 +12705,7 @@
         <v>265</v>
       </c>
       <c r="M280" s="7" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="281" spans="1:13" x14ac:dyDescent="0.4">
@@ -12713,7 +12713,7 @@
         <v>266</v>
       </c>
       <c r="M281" s="7" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="282" spans="1:13" x14ac:dyDescent="0.4">
@@ -12721,7 +12721,7 @@
         <v>267</v>
       </c>
       <c r="M282" s="7" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="283" spans="1:13" x14ac:dyDescent="0.4">
@@ -12729,7 +12729,7 @@
         <v>268</v>
       </c>
       <c r="M283" s="7" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="284" spans="1:13" x14ac:dyDescent="0.4">
@@ -12737,7 +12737,7 @@
         <v>269</v>
       </c>
       <c r="M284" s="7" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="285" spans="1:13" x14ac:dyDescent="0.4">
@@ -12745,7 +12745,7 @@
         <v>270</v>
       </c>
       <c r="M285" s="7" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="286" spans="1:13" x14ac:dyDescent="0.4">
@@ -12753,50 +12753,50 @@
         <v>271</v>
       </c>
       <c r="M286" s="7" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="287" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B287" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C287" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D287" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E287" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F287" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G287" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="H287" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="I287" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J287" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="K287" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="L287" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="288" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A288" s="9" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="M288" s="7" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="289" spans="1:13" x14ac:dyDescent="0.4">
@@ -12804,7 +12804,7 @@
         <v>272</v>
       </c>
       <c r="M289" s="7" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="290" spans="1:13" x14ac:dyDescent="0.4">
@@ -12812,7 +12812,7 @@
         <v>273</v>
       </c>
       <c r="M290" s="7" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="291" spans="1:13" x14ac:dyDescent="0.4">
@@ -12820,7 +12820,7 @@
         <v>274</v>
       </c>
       <c r="M291" s="7" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="292" spans="1:13" x14ac:dyDescent="0.4">
@@ -12828,7 +12828,7 @@
         <v>275</v>
       </c>
       <c r="M292" s="7" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="293" spans="1:13" x14ac:dyDescent="0.4">
@@ -12836,7 +12836,7 @@
         <v>276</v>
       </c>
       <c r="M293" s="7" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="294" spans="1:13" x14ac:dyDescent="0.4">
@@ -12844,7 +12844,7 @@
         <v>277</v>
       </c>
       <c r="M294" s="7" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="295" spans="1:13" x14ac:dyDescent="0.4">
@@ -12852,7 +12852,7 @@
         <v>278</v>
       </c>
       <c r="M295" s="7" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="296" spans="1:13" x14ac:dyDescent="0.4">
@@ -12860,7 +12860,7 @@
         <v>279</v>
       </c>
       <c r="M296" s="7" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
     </row>
     <row r="297" spans="1:13" x14ac:dyDescent="0.4">
@@ -12868,7 +12868,7 @@
         <v>280</v>
       </c>
       <c r="M297" s="7" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="298" spans="1:13" x14ac:dyDescent="0.4">
@@ -12876,7 +12876,7 @@
         <v>281</v>
       </c>
       <c r="M298" s="7" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="299" spans="1:13" x14ac:dyDescent="0.4">
@@ -12884,7 +12884,7 @@
         <v>282</v>
       </c>
       <c r="M299" s="7" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="300" spans="1:13" x14ac:dyDescent="0.4">
@@ -12892,7 +12892,7 @@
         <v>283</v>
       </c>
       <c r="M300" s="7" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="301" spans="1:13" x14ac:dyDescent="0.4">
@@ -12900,7 +12900,7 @@
         <v>284</v>
       </c>
       <c r="M301" s="7" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="302" spans="1:13" x14ac:dyDescent="0.4">
@@ -12908,7 +12908,7 @@
         <v>285</v>
       </c>
       <c r="M302" s="7" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="303" spans="1:13" x14ac:dyDescent="0.4">
@@ -12916,7 +12916,7 @@
         <v>286</v>
       </c>
       <c r="M303" s="7" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="304" spans="1:13" x14ac:dyDescent="0.4">
@@ -12924,7 +12924,7 @@
         <v>287</v>
       </c>
       <c r="M304" s="7" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="305" spans="1:13" x14ac:dyDescent="0.4">
@@ -12932,7 +12932,7 @@
         <v>288</v>
       </c>
       <c r="M305" s="7" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="306" spans="1:13" x14ac:dyDescent="0.4">
@@ -12940,7 +12940,7 @@
         <v>289</v>
       </c>
       <c r="M306" s="7" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="307" spans="1:13" x14ac:dyDescent="0.4">
@@ -12948,7 +12948,7 @@
         <v>290</v>
       </c>
       <c r="M307" s="7" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="308" spans="1:13" x14ac:dyDescent="0.4">
@@ -12956,7 +12956,7 @@
         <v>291</v>
       </c>
       <c r="M308" s="7" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="309" spans="1:13" x14ac:dyDescent="0.4">
@@ -12964,7 +12964,7 @@
         <v>292</v>
       </c>
       <c r="M309" s="7" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="310" spans="1:13" x14ac:dyDescent="0.4">
@@ -12972,7 +12972,7 @@
         <v>293</v>
       </c>
       <c r="M310" s="7" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
     </row>
     <row r="311" spans="1:13" x14ac:dyDescent="0.4">
@@ -12980,7 +12980,7 @@
         <v>294</v>
       </c>
       <c r="M311" s="7" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="312" spans="1:13" x14ac:dyDescent="0.4">
@@ -12988,7 +12988,7 @@
         <v>295</v>
       </c>
       <c r="M312" s="7" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="313" spans="1:13" x14ac:dyDescent="0.4">
@@ -12996,7 +12996,7 @@
         <v>296</v>
       </c>
       <c r="M313" s="7" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="314" spans="1:13" x14ac:dyDescent="0.4">
@@ -13004,7 +13004,7 @@
         <v>297</v>
       </c>
       <c r="M314" s="7" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="315" spans="1:13" x14ac:dyDescent="0.4">
@@ -13012,7 +13012,7 @@
         <v>298</v>
       </c>
       <c r="M315" s="7" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
     </row>
     <row r="316" spans="1:13" x14ac:dyDescent="0.4">
@@ -13020,7 +13020,7 @@
         <v>299</v>
       </c>
       <c r="M316" s="7" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
     </row>
     <row r="317" spans="1:13" x14ac:dyDescent="0.4">
@@ -13028,50 +13028,50 @@
         <v>300</v>
       </c>
       <c r="M317" s="7" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
     </row>
     <row r="318" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B318" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C318" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D318" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E318" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F318" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G318" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="H318" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="I318" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J318" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="K318" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="L318" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="319" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A319" s="10" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="M319" s="7" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
     </row>
     <row r="320" spans="1:13" x14ac:dyDescent="0.4">
@@ -13079,7 +13079,7 @@
         <v>301</v>
       </c>
       <c r="M320" s="7" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
     </row>
     <row r="321" spans="1:13" x14ac:dyDescent="0.4">
@@ -13087,7 +13087,7 @@
         <v>302</v>
       </c>
       <c r="M321" s="7" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
     </row>
     <row r="322" spans="1:13" x14ac:dyDescent="0.4">
@@ -13095,7 +13095,7 @@
         <v>303</v>
       </c>
       <c r="M322" s="7" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="323" spans="1:13" x14ac:dyDescent="0.4">
@@ -13103,7 +13103,7 @@
         <v>304</v>
       </c>
       <c r="M323" s="7" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="324" spans="1:13" x14ac:dyDescent="0.4">
@@ -13111,7 +13111,7 @@
         <v>305</v>
       </c>
       <c r="M324" s="7" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="325" spans="1:13" x14ac:dyDescent="0.4">
@@ -13119,7 +13119,7 @@
         <v>306</v>
       </c>
       <c r="M325" s="7" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="326" spans="1:13" x14ac:dyDescent="0.4">
@@ -13127,7 +13127,7 @@
         <v>307</v>
       </c>
       <c r="M326" s="7" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="327" spans="1:13" x14ac:dyDescent="0.4">
@@ -13135,7 +13135,7 @@
         <v>308</v>
       </c>
       <c r="M327" s="7" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="328" spans="1:13" x14ac:dyDescent="0.4">
@@ -13143,7 +13143,7 @@
         <v>309</v>
       </c>
       <c r="M328" s="7" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="329" spans="1:13" x14ac:dyDescent="0.4">
@@ -13151,7 +13151,7 @@
         <v>310</v>
       </c>
       <c r="M329" s="7" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="330" spans="1:13" x14ac:dyDescent="0.4">
@@ -13159,7 +13159,7 @@
         <v>311</v>
       </c>
       <c r="M330" s="7" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="331" spans="1:13" x14ac:dyDescent="0.4">
@@ -13167,7 +13167,7 @@
         <v>312</v>
       </c>
       <c r="M331" s="7" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="332" spans="1:13" x14ac:dyDescent="0.4">
@@ -13175,7 +13175,7 @@
         <v>313</v>
       </c>
       <c r="M332" s="7" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
     </row>
     <row r="333" spans="1:13" x14ac:dyDescent="0.4">
@@ -13183,7 +13183,7 @@
         <v>314</v>
       </c>
       <c r="M333" s="7" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="334" spans="1:13" x14ac:dyDescent="0.4">
@@ -13191,7 +13191,7 @@
         <v>315</v>
       </c>
       <c r="M334" s="7" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="335" spans="1:13" x14ac:dyDescent="0.4">
@@ -13199,7 +13199,7 @@
         <v>316</v>
       </c>
       <c r="M335" s="7" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
     <row r="336" spans="1:13" x14ac:dyDescent="0.4">
@@ -13207,7 +13207,7 @@
         <v>317</v>
       </c>
       <c r="M336" s="7" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
     </row>
     <row r="337" spans="1:13" x14ac:dyDescent="0.4">
@@ -13215,7 +13215,7 @@
         <v>318</v>
       </c>
       <c r="M337" s="7" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="338" spans="1:13" x14ac:dyDescent="0.4">
@@ -13223,7 +13223,7 @@
         <v>319</v>
       </c>
       <c r="M338" s="7" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
     </row>
     <row r="339" spans="1:13" x14ac:dyDescent="0.4">
@@ -13231,7 +13231,7 @@
         <v>320</v>
       </c>
       <c r="M339" s="7" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
     </row>
     <row r="340" spans="1:13" x14ac:dyDescent="0.4">
@@ -13239,7 +13239,7 @@
         <v>321</v>
       </c>
       <c r="M340" s="7" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
     </row>
     <row r="341" spans="1:13" x14ac:dyDescent="0.4">
@@ -13247,7 +13247,7 @@
         <v>322</v>
       </c>
       <c r="M341" s="7" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
     </row>
     <row r="342" spans="1:13" x14ac:dyDescent="0.4">
@@ -13255,7 +13255,7 @@
         <v>323</v>
       </c>
       <c r="M342" s="7" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="343" spans="1:13" x14ac:dyDescent="0.4">
@@ -13263,7 +13263,7 @@
         <v>324</v>
       </c>
       <c r="M343" s="7" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="344" spans="1:13" x14ac:dyDescent="0.4">
@@ -13271,7 +13271,7 @@
         <v>325</v>
       </c>
       <c r="M344" s="7" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="345" spans="1:13" x14ac:dyDescent="0.4">
@@ -13279,7 +13279,7 @@
         <v>326</v>
       </c>
       <c r="M345" s="7" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="346" spans="1:13" x14ac:dyDescent="0.4">
@@ -13287,7 +13287,7 @@
         <v>327</v>
       </c>
       <c r="M346" s="7" t="s">
-        <v>681</v>
+        <v>733</v>
       </c>
     </row>
     <row r="347" spans="1:13" x14ac:dyDescent="0.4">
@@ -13295,7 +13295,7 @@
         <v>328</v>
       </c>
       <c r="M347" s="7" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
     </row>
     <row r="348" spans="1:13" x14ac:dyDescent="0.4">
@@ -13303,50 +13303,50 @@
         <v>329</v>
       </c>
       <c r="M348" s="7" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
     </row>
     <row r="349" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B349" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C349" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D349" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E349" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F349" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G349" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="H349" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="I349" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J349" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="K349" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="L349" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="350" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A350" s="11" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="M350" s="7" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
     </row>
     <row r="351" spans="1:13" x14ac:dyDescent="0.4">
@@ -13354,7 +13354,7 @@
         <v>330</v>
       </c>
       <c r="M351" s="7" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
     </row>
     <row r="352" spans="1:13" x14ac:dyDescent="0.4">
@@ -13362,7 +13362,7 @@
         <v>331</v>
       </c>
       <c r="M352" s="7" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
     </row>
     <row r="353" spans="1:13" x14ac:dyDescent="0.4">
@@ -13370,7 +13370,7 @@
         <v>332</v>
       </c>
       <c r="M353" s="7" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="354" spans="1:13" x14ac:dyDescent="0.4">
@@ -13378,7 +13378,7 @@
         <v>333</v>
       </c>
       <c r="M354" s="7" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
     </row>
     <row r="355" spans="1:13" x14ac:dyDescent="0.4">
@@ -13386,7 +13386,7 @@
         <v>334</v>
       </c>
       <c r="M355" s="7" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="356" spans="1:13" x14ac:dyDescent="0.4">
@@ -13394,7 +13394,7 @@
         <v>335</v>
       </c>
       <c r="M356" s="7" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
     </row>
     <row r="357" spans="1:13" x14ac:dyDescent="0.4">
@@ -13402,7 +13402,7 @@
         <v>336</v>
       </c>
       <c r="M357" s="7" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="358" spans="1:13" x14ac:dyDescent="0.4">
@@ -13410,7 +13410,7 @@
         <v>337</v>
       </c>
       <c r="M358" s="7" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
     </row>
     <row r="359" spans="1:13" x14ac:dyDescent="0.4">
@@ -13418,7 +13418,7 @@
         <v>338</v>
       </c>
       <c r="M359" s="7" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
     </row>
     <row r="360" spans="1:13" x14ac:dyDescent="0.4">
@@ -13426,7 +13426,7 @@
         <v>339</v>
       </c>
       <c r="M360" s="7" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
     </row>
     <row r="361" spans="1:13" x14ac:dyDescent="0.4">
@@ -13434,7 +13434,7 @@
         <v>340</v>
       </c>
       <c r="M361" s="7" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
     </row>
     <row r="362" spans="1:13" x14ac:dyDescent="0.4">
@@ -13442,7 +13442,7 @@
         <v>341</v>
       </c>
       <c r="M362" s="7" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
     </row>
     <row r="363" spans="1:13" x14ac:dyDescent="0.4">
@@ -13450,7 +13450,7 @@
         <v>342</v>
       </c>
       <c r="M363" s="7" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
     </row>
     <row r="364" spans="1:13" x14ac:dyDescent="0.4">
@@ -13458,7 +13458,7 @@
         <v>343</v>
       </c>
       <c r="M364" s="7" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="365" spans="1:13" x14ac:dyDescent="0.4">
@@ -13466,7 +13466,7 @@
         <v>344</v>
       </c>
       <c r="M365" s="7" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
     </row>
     <row r="366" spans="1:13" x14ac:dyDescent="0.4">
@@ -13474,7 +13474,7 @@
         <v>345</v>
       </c>
       <c r="M366" s="7" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
     </row>
     <row r="367" spans="1:13" x14ac:dyDescent="0.4">
@@ -13482,7 +13482,7 @@
         <v>346</v>
       </c>
       <c r="M367" s="7" t="s">
-        <v>701</v>
+        <v>734</v>
       </c>
     </row>
     <row r="368" spans="1:13" x14ac:dyDescent="0.4">
@@ -13490,7 +13490,7 @@
         <v>347</v>
       </c>
       <c r="M368" s="7" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
     </row>
     <row r="369" spans="1:13" x14ac:dyDescent="0.4">
@@ -13498,7 +13498,7 @@
         <v>348</v>
       </c>
       <c r="M369" s="7" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
     </row>
     <row r="370" spans="1:13" x14ac:dyDescent="0.4">
@@ -13506,7 +13506,7 @@
         <v>349</v>
       </c>
       <c r="M370" s="7" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
     </row>
     <row r="371" spans="1:13" x14ac:dyDescent="0.4">
@@ -13514,7 +13514,7 @@
         <v>350</v>
       </c>
       <c r="M371" s="7" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
     </row>
     <row r="372" spans="1:13" x14ac:dyDescent="0.4">
@@ -13522,7 +13522,7 @@
         <v>351</v>
       </c>
       <c r="M372" s="7" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
     </row>
     <row r="373" spans="1:13" x14ac:dyDescent="0.4">
@@ -13530,7 +13530,7 @@
         <v>352</v>
       </c>
       <c r="M373" s="7" t="s">
-        <v>707</v>
+        <v>738</v>
       </c>
     </row>
     <row r="374" spans="1:13" x14ac:dyDescent="0.4">
@@ -13538,7 +13538,7 @@
         <v>353</v>
       </c>
       <c r="M374" s="7" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
     </row>
     <row r="375" spans="1:13" x14ac:dyDescent="0.4">
@@ -13546,7 +13546,7 @@
         <v>354</v>
       </c>
       <c r="M375" s="7" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
     </row>
     <row r="376" spans="1:13" x14ac:dyDescent="0.4">
@@ -13554,7 +13554,7 @@
         <v>355</v>
       </c>
       <c r="M376" s="7" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
     </row>
     <row r="377" spans="1:13" x14ac:dyDescent="0.4">
@@ -13562,7 +13562,7 @@
         <v>356</v>
       </c>
       <c r="M377" s="7" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
     </row>
     <row r="378" spans="1:13" x14ac:dyDescent="0.4">
@@ -13570,7 +13570,7 @@
         <v>357</v>
       </c>
       <c r="M378" s="7" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
     </row>
     <row r="379" spans="1:13" x14ac:dyDescent="0.4">
@@ -13578,48 +13578,48 @@
         <v>358</v>
       </c>
       <c r="M379" s="7" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
     </row>
     <row r="380" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A380" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="B380" s="8" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="C380" s="8" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="D380" s="8" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="E380" s="8" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="F380" s="8" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="G380" s="8" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="H380" s="8" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="I380" s="8" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="J380" s="8" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="K380" s="8" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="L380" s="8" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="M380" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
     </row>
   </sheetData>
